--- a/sports_forms/039_football_trial_application_form--sports_forms.xlsx
+++ b/sports_forms/039_football_trial_application_form--sports_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -505,17 +505,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>football_trial_application_form_page_1</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>football_trial_application_form_page_1</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,13 +538,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>trial_details</t>
+          <t>Trial Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -561,13 +561,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>trial_dates</t>
+          <t>Trial Dates</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -584,13 +584,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>trial_time</t>
+          <t>Trial Time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>trial_location</t>
+          <t>Trial Location</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -620,17 +620,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>trial_notes</t>
+          <t>football_player_details</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>trial_notes</t>
+          <t>Football Player Details</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>trial_attorney</t>
+          <t>Trial Attorney</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>football_player_details</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>football_player_details</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -689,159 +689,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>trial_date</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>trial_date</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>trial_time</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>trial_time</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>trial_location</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>trial_location</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>trial_attorney</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>trial_attorney</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>trial_notes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>trial_notes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>football_player_details</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>football_player_details</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
